--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484339_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484339_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1842</v>
+        <v>3.4801</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6067</v>
+        <v>4.2022</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4225</v>
+        <v>-0.7221</v>
       </c>
       <c r="G2" t="n">
         <v>1.5461</v>
@@ -610,13 +610,13 @@
         <v>3.5162</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5107</v>
+        <v>-1.2147</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1515</v>
+        <v>-0.2529</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6622</v>
+        <v>-0.9618</v>
       </c>
       <c r="V2" t="n">
         <v>0.6093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8889</v>
+        <v>3.0717</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8932</v>
+        <v>2.9943</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0044</v>
+        <v>0.0774</v>
       </c>
       <c r="G3" t="n">
         <v>2.9673</v>
@@ -688,13 +688,13 @@
         <v>0.7814</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2152</v>
+        <v>-0.0323</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1486</v>
+        <v>0.2497</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3638</v>
+        <v>-0.2821</v>
       </c>
       <c r="V3" t="n">
         <v>0.3321</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6941</v>
+        <v>2.943</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0737</v>
+        <v>1.3771</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6204</v>
+        <v>1.5659</v>
       </c>
       <c r="G4" t="n">
         <v>4.4145</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9938</v>
+        <v>-0.745</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6382</v>
+        <v>-0.3349</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3556</v>
+        <v>-0.4101</v>
       </c>
       <c r="V4" t="n">
         <v>0.0549</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9491000000000001</v>
+        <v>1.1592</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8349</v>
+        <v>-0.7337</v>
       </c>
       <c r="F5" t="n">
-        <v>1.784</v>
+        <v>1.8929</v>
       </c>
       <c r="G5" t="n">
         <v>0.007</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.23</v>
+        <v>-0.0199</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3026</v>
+        <v>-0.2015</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0726</v>
+        <v>0.1816</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5685</v>
+        <v>0.7864</v>
       </c>
       <c r="E6" t="n">
         <v>1.5272</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9587</v>
+        <v>-0.7408</v>
       </c>
       <c r="G6" t="n">
         <v>1.4467</v>
@@ -922,13 +922,13 @@
         <v>3.5162</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4642</v>
+        <v>-1.2464</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1457</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3186</v>
+        <v>-1.1007</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>P. TABERNER PERALTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4262</v>
+        <v>-0.775</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8843</v>
+        <v>-0.5726</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4581</v>
+        <v>-0.2023</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3724</v>
+        <v>-0.4881</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2732</v>
+        <v>0.3346</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6457</v>
+        <v>-0.8227</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4083</v>
+        <v>-0.5527</v>
       </c>
       <c r="K7" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4313</v>
+        <v>-0.5527</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9641</v>
+        <v>0.0646</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2502</v>
+        <v>0.3346</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2144</v>
+        <v>-0.27</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.077</v>
+        <v>-0.2869</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2588</v>
+        <v>-0.0199</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3358</v>
+        <v>-0.2669</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. TABERNER PERALTA</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8216</v>
+        <v>-0.8756</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6737</v>
+        <v>-1.6499</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1479</v>
+        <v>0.7744</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4881</v>
+        <v>-0.8116</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3346</v>
+        <v>-0.3937</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8227</v>
+        <v>-0.4179</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5527</v>
+        <v>-0.5322</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
         <v>-0.5527</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0646</v>
+        <v>-0.2793</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3346</v>
+        <v>-0.4142</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.27</v>
+        <v>0.1348</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3335</v>
+        <v>-0.2593</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.121</v>
+        <v>-0.141</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2125</v>
+        <v>-0.1183</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>J. REDA COLL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0311</v>
+        <v>-1.1507</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.751</v>
+        <v>-1.2715</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7199</v>
+        <v>0.1208</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8116</v>
+        <v>2.1884</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3937</v>
+        <v>0.4741</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4179</v>
+        <v>1.7144</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5322</v>
+        <v>3.9163</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0205</v>
+        <v>1.3917</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5527</v>
+        <v>2.5247</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2793</v>
+        <v>-1.7279</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4142</v>
+        <v>-0.9176</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1348</v>
+        <v>-0.8103</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>3.1255</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4149</v>
+        <v>-1.8936</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2421</v>
+        <v>-0.6168</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1728</v>
+        <v>-1.2768</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. REDA COLL</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6563</v>
+        <v>-1.2702</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7771</v>
+        <v>-1.5921</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1208</v>
+        <v>0.322</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1884</v>
+        <v>-1.3724</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4741</v>
+        <v>0.2732</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7144</v>
+        <v>-1.6457</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9163</v>
+        <v>-0.4083</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3917</v>
+        <v>0.023</v>
       </c>
       <c r="L10" t="n">
-        <v>2.5247</v>
+        <v>-0.4313</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7279</v>
+        <v>-0.9641</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9176</v>
+        <v>0.2502</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8103</v>
+        <v>-1.2144</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1255</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3992</v>
+        <v>-0.921</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1224</v>
+        <v>-0.449</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2768</v>
+        <v>-0.472</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9172</v>
+        <v>-1.8549</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2265</v>
+        <v>0.1254</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1438</v>
+        <v>-1.9804</v>
       </c>
       <c r="G11" t="n">
         <v>0.7609</v>
@@ -1312,13 +1312,13 @@
         <v>2.3441</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.905</v>
+        <v>-1.8427</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.7447</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2614</v>
+        <v>-1.098</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1638</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3237</v>
+        <v>-2.4054</v>
       </c>
       <c r="E12" t="n">
         <v>-2.0135</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3102</v>
+        <v>-0.3919</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9624</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3846</v>
+        <v>-0.4663</v>
       </c>
       <c r="T12" t="n">
         <v>-0.4237</v>
       </c>
       <c r="U12" t="n">
-        <v>0.039</v>
+        <v>-0.0427</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1087</v>
+        <v>3.108599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.392800000000001</v>
+        <v>2.3929</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7157</v>
+        <v>0.7159000000000005</v>
       </c>
       <c r="G13" t="n">
         <v>9.696399999999997</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2745</v>
+        <v>2.274500000000001</v>
       </c>
       <c r="I13" t="n">
         <v>7.4222</v>
@@ -1444,7 +1444,7 @@
         <v>18.012</v>
       </c>
       <c r="K13" t="n">
-        <v>5.189500000000001</v>
+        <v>5.1895</v>
       </c>
       <c r="L13" t="n">
         <v>12.8228</v>
@@ -1456,10 +1456,10 @@
         <v>-2.9149</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.400699999999999</v>
+        <v>-5.4007</v>
       </c>
       <c r="P13" t="n">
-        <v>1.953499999999999</v>
+        <v>1.9535</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.5807</v>
@@ -1474,13 +1474,13 @@
         <v>-3.0804</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.8479</v>
+        <v>-5.847799999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.3869</v>
       </c>
       <c r="W13" t="n">
-        <v>5.041899999999999</v>
+        <v>5.0419</v>
       </c>
       <c r="X13" t="n">
         <v>-4.6551</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3189</v>
+        <v>6.9315</v>
       </c>
       <c r="E14" t="n">
-        <v>8.6913</v>
+        <v>7.6802</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3724</v>
+        <v>-0.7487</v>
       </c>
       <c r="G14" t="n">
         <v>0.4844</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9833</v>
+        <v>1.5958</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2535</v>
+        <v>1.2424</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2703</v>
+        <v>0.3534</v>
       </c>
       <c r="V14" t="n">
         <v>4.2652</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6341</v>
+        <v>3.6069</v>
       </c>
       <c r="E15" t="n">
         <v>1.3147</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3194</v>
+        <v>2.2922</v>
       </c>
       <c r="G15" t="n">
         <v>0.7026</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5679</v>
+        <v>0.5406</v>
       </c>
       <c r="T15" t="n">
         <v>0.2504</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3174</v>
+        <v>0.2902</v>
       </c>
       <c r="V15" t="n">
         <v>0.9962</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.32</v>
+        <v>-0.1659</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7885</v>
+        <v>-0.141</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1086</v>
+        <v>-0.0249</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6005</v>
+        <v>-3.2805</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3541</v>
+        <v>-1.7839</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9546</v>
+        <v>-1.4966</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8999</v>
+        <v>-0.6322</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7304</v>
+        <v>-1.1602</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6303</v>
+        <v>0.528</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2994</v>
+        <v>-2.6484</v>
       </c>
       <c r="N16" t="n">
         <v>-0.6237</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6757</v>
+        <v>-2.0247</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.3208</v>
+        <v>2.1488</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.8603</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>3.1255</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3725</v>
+        <v>1.5752</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8947</v>
+        <v>0.8586</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4778</v>
+        <v>0.7166</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3321</v>
+        <v>-0.6093</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6621</v>
+        <v>-0.5507</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1964</v>
+        <v>-2.3053</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8585</v>
+        <v>1.7545</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5662</v>
+        <v>0.6005</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2011</v>
+        <v>-1.3541</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7673</v>
+        <v>1.9546</v>
       </c>
       <c r="J17" t="n">
-        <v>0.532</v>
+        <v>1.8999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4106</v>
+        <v>-0.7304</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1214</v>
+        <v>2.6303</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0982</v>
+        <v>-1.2994</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2095</v>
+        <v>-0.6237</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8887</v>
+        <v>-0.6757</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-5.8603</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0994</v>
+        <v>2.5017</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8365</v>
+        <v>1.3779</v>
       </c>
       <c r="U17" t="n">
-        <v>0.263</v>
+        <v>1.1237</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8672</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5454</v>
+        <v>-0.0341</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3218</v>
+        <v>-0.8142</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.2805</v>
+        <v>-1.933</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7839</v>
+        <v>0.549</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4966</v>
+        <v>-2.482</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6322</v>
+        <v>-0.244</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1602</v>
+        <v>0.3492</v>
       </c>
       <c r="L18" t="n">
-        <v>0.528</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6484</v>
+        <v>-1.6891</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6237</v>
+        <v>0.1998</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0247</v>
+        <v>-1.8889</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1255</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8738</v>
+        <v>0.3033</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4541</v>
+        <v>0.2098</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4197</v>
+        <v>0.0935</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3696</v>
+        <v>-1.0304</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3375</v>
+        <v>0.4644</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0321</v>
+        <v>-1.4948</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.933</v>
+        <v>1.5167</v>
       </c>
       <c r="H19" t="n">
-        <v>0.549</v>
+        <v>0.7897</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.482</v>
+        <v>0.727</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.244</v>
+        <v>4.5744</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3492</v>
+        <v>1.8227</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>2.7517</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6891</v>
+        <v>-3.0577</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1998</v>
+        <v>-1.033</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8889</v>
+        <v>-2.0247</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>2.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2179</v>
+        <v>0.9217</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0935</v>
+        <v>0.461</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1244</v>
+        <v>0.4607</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.4921</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8093</v>
+        <v>-1.1755</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3454</v>
+        <v>-0.2081</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5361</v>
+        <v>-0.9674</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3389</v>
+        <v>-1.5662</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8261</v>
+        <v>0.2011</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5128</v>
+        <v>-1.7673</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5841</v>
+        <v>0.532</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6117</v>
+        <v>0.4106</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0276</v>
+        <v>0.1214</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7548</v>
+        <v>-2.0982</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2144</v>
+        <v>-0.2095</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5405</v>
+        <v>-1.8887</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5395</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2524</v>
+        <v>0.586</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5009</v>
+        <v>0.432</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.154</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8518</v>
+        <v>-1.5876</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9512</v>
+        <v>-4.0421</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9006</v>
+        <v>2.4544</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5167</v>
+        <v>-2.3389</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7897</v>
+        <v>-1.8261</v>
       </c>
       <c r="I21" t="n">
-        <v>0.727</v>
+        <v>-0.5128</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5744</v>
+        <v>-1.5841</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8227</v>
+        <v>-1.6117</v>
       </c>
       <c r="L21" t="n">
-        <v>2.7517</v>
+        <v>0.0276</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.0577</v>
+        <v>-0.7548</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.033</v>
+        <v>-0.2144</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0247</v>
+        <v>-0.5405</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9301</v>
+        <v>2.5395</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8997000000000001</v>
+        <v>1.474</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9546</v>
+        <v>0.8042</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0549</v>
+        <v>0.6698</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4921</v>
+        <v>-0.3321</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6642</v>
+        <v>-0.3321</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8339</v>
+        <v>-3.4437</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5377</v>
+        <v>-2.3354</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2962</v>
+        <v>-1.1083</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1129</v>
@@ -2170,13 +2170,13 @@
         <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0215</v>
+        <v>0.3687</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.033</v>
+        <v>0.1693</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0115</v>
+        <v>0.1994</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9414</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9878</v>
+        <v>-3.4966</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4125</v>
+        <v>-1.1091</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5754</v>
+        <v>-2.3875</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7691</v>
@@ -2248,13 +2248,13 @@
         <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.082</v>
+        <v>0.4093</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2613</v>
+        <v>0.0421</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1793</v>
+        <v>0.3672</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9414</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1087</v>
+        <v>-1.7603</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7158000000000002</v>
+        <v>-0.7158</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3929</v>
+        <v>-1.0447</v>
       </c>
       <c r="G24" t="n">
         <v>-9.696400000000001</v>
@@ -2299,10 +2299,10 @@
         <v>-7.4219</v>
       </c>
       <c r="J24" t="n">
-        <v>8.315599999999998</v>
+        <v>8.3156</v>
       </c>
       <c r="K24" t="n">
-        <v>2.914900000000001</v>
+        <v>2.9149</v>
       </c>
       <c r="L24" t="n">
         <v>5.4006</v>
@@ -2326,13 +2326,13 @@
         <v>17.5809</v>
       </c>
       <c r="S24" t="n">
-        <v>8.928199999999999</v>
+        <v>10.2763</v>
       </c>
       <c r="T24" t="n">
-        <v>5.847699999999999</v>
+        <v>5.8477</v>
       </c>
       <c r="U24" t="n">
-        <v>3.0804</v>
+        <v>4.428500000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-0.387</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484339_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484339_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.6551</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,11 +1624,16 @@
       <c r="X14" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6069</v>
+        <v>3.6559</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3147</v>
+        <v>3.6559</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2922</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7026</v>
+        <v>3.6559</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8378</v>
+        <v>1.2279</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1352</v>
+        <v>2.4279</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9824000000000001</v>
+        <v>3.6559</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.2279</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.4279</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2797</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1445</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1352</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5406</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2504</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2902</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9962</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.719</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1659</v>
+        <v>3.6069</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.141</v>
+        <v>1.3147</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0249</v>
+        <v>2.2922</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.2805</v>
+        <v>0.7026</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7839</v>
+        <v>0.8378</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4966</v>
+        <v>-0.1352</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6322</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1602</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6484</v>
+        <v>-0.2797</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6237</v>
+        <v>-0.1445</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0247</v>
+        <v>-0.1352</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1255</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5752</v>
+        <v>0.5406</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8586</v>
+        <v>0.2504</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7166</v>
+        <v>0.2902</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>0.9962</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0.719</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5507</v>
+        <v>0.307</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3053</v>
+        <v>0.307</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7545</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6005</v>
+        <v>0.307</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3541</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9546</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8999</v>
+        <v>0.307</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7304</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6303</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2994</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6237</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6757</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.3208</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.8603</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5017</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3779</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1237</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.1659</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0341</v>
+        <v>-0.141</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8142</v>
+        <v>-0.0249</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.933</v>
+        <v>-3.2805</v>
       </c>
       <c r="H18" t="n">
-        <v>0.549</v>
+        <v>-1.7839</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.482</v>
+        <v>-1.4966</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.244</v>
+        <v>-0.6322</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3492</v>
+        <v>-1.1602</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.528</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6891</v>
+        <v>-2.6484</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1998</v>
+        <v>-0.6237</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8889</v>
+        <v>-2.0247</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>3.1255</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3033</v>
+        <v>1.5752</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2098</v>
+        <v>0.8586</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0935</v>
+        <v>0.7166</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0304</v>
+        <v>-0.5507</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4644</v>
+        <v>-2.3053</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4948</v>
+        <v>1.7545</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5167</v>
+        <v>0.6005</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7897</v>
+        <v>-1.3541</v>
       </c>
       <c r="I19" t="n">
-        <v>0.727</v>
+        <v>1.9546</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5744</v>
+        <v>1.8999</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8227</v>
+        <v>-0.7304</v>
       </c>
       <c r="L19" t="n">
-        <v>2.7517</v>
+        <v>2.6303</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0577</v>
+        <v>-1.2994</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.033</v>
+        <v>-0.6237</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0247</v>
+        <v>-0.6757</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.9069</v>
+        <v>-5.8603</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9301</v>
+        <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9217</v>
+        <v>2.5017</v>
       </c>
       <c r="T19" t="n">
-        <v>0.461</v>
+        <v>1.3779</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4607</v>
+        <v>1.1237</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4921</v>
+        <v>-0.3321</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8279</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1755</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2081</v>
+        <v>-0.0341</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9674</v>
+        <v>-0.8142</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5662</v>
+        <v>-1.933</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2011</v>
+        <v>0.549</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7673</v>
+        <v>-2.482</v>
       </c>
       <c r="J20" t="n">
-        <v>0.532</v>
+        <v>-0.244</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4106</v>
+        <v>0.3492</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1214</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0982</v>
+        <v>-1.6891</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2095</v>
+        <v>0.1998</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8887</v>
+        <v>-1.8889</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>0.586</v>
+        <v>0.3033</v>
       </c>
       <c r="T20" t="n">
-        <v>0.432</v>
+        <v>0.2098</v>
       </c>
       <c r="U20" t="n">
-        <v>0.154</v>
+        <v>0.0935</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,12 +2121,17 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5876</v>
+        <v>-1.1755</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.0421</v>
+        <v>-0.2081</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4544</v>
+        <v>-0.9674</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3389</v>
+        <v>-1.5662</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8261</v>
+        <v>0.2011</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5128</v>
+        <v>-1.7673</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5841</v>
+        <v>0.532</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6117</v>
+        <v>0.4106</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0276</v>
+        <v>0.1214</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7548</v>
+        <v>-2.0982</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2144</v>
+        <v>-0.2095</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5405</v>
+        <v>-1.8887</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5395</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>1.474</v>
+        <v>0.586</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8042</v>
+        <v>0.432</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6698</v>
+        <v>0.154</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4437</v>
+        <v>-1.8946</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3354</v>
+        <v>-4.3491</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1083</v>
+        <v>2.4544</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1129</v>
+        <v>-2.6459</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1686</v>
+        <v>-2.1331</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9443</v>
+        <v>-0.5128</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6332</v>
+        <v>-1.8911</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0409</v>
+        <v>-1.9187</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6741</v>
+        <v>0.0276</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4797</v>
+        <v>-0.7548</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2095</v>
+        <v>-0.2144</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2702</v>
+        <v>-0.5405</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1488</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3687</v>
+        <v>1.474</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1693</v>
+        <v>0.8042</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1994</v>
+        <v>0.6698</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9414</v>
+        <v>-0.3321</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4966</v>
+        <v>-3.4437</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1091</v>
+        <v>-2.3354</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3875</v>
+        <v>-1.1083</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7691</v>
+        <v>-1.1129</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9862</v>
+        <v>-0.1686</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7829</v>
+        <v>-0.9443</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2563</v>
+        <v>-0.6332</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9581</v>
+        <v>0.0409</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7017</v>
+        <v>-0.6741</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5127</v>
+        <v>-0.4797</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0281</v>
+        <v>-0.2095</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4846</v>
+        <v>-0.2702</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1953</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4093</v>
+        <v>0.3687</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0421</v>
+        <v>0.1693</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3672</v>
+        <v>0.1994</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9414</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7603</v>
+        <v>-3.4966</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7158</v>
+        <v>-1.1091</v>
       </c>
       <c r="F24" t="n">
+        <v>-2.3875</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.7691</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.9862</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.7829</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.2563</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.9581</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.7017</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.5127</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.0281</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.4846</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.9414</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P. CABANERO PUERTAS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.6863</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.1915</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.4948</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.1392</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.4382</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.7009</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9185</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.5948</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-3.0577</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.033</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-2.0247</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.9217</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.4607</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-2.4921</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484339_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.760300000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.7157999999999984</v>
+      </c>
+      <c r="F26" t="n">
         <v>-1.0447</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>-9.696400000000001</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>-2.2744</v>
       </c>
-      <c r="I24" t="n">
-        <v>-7.4219</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="I26" t="n">
+        <v>-7.421899999999999</v>
+      </c>
+      <c r="J26" t="n">
         <v>8.3156</v>
       </c>
-      <c r="K24" t="n">
-        <v>2.9149</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5.4006</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="K26" t="n">
+        <v>2.914899999999999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>5.400499999999999</v>
+      </c>
+      <c r="M26" t="n">
         <v>-18.012</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-5.1892</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>-12.8229</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>-1.9533</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-19.5344</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>17.5809</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>10.2763</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>5.8477</v>
       </c>
-      <c r="U24" t="n">
-        <v>4.428500000000001</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="U26" t="n">
+        <v>4.4285</v>
+      </c>
+      <c r="V26" t="n">
         <v>-0.387</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>4.6549</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-5.0419</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
